--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6430,0.0185,0.2048,0.0785</t>
-  </si>
-  <si>
-    <t>0.6486,0.0064,0.1274,0.0976</t>
-  </si>
-  <si>
-    <t>0.4668,0.0320,0.1621,0.3973</t>
-  </si>
-  <si>
-    <t>0.5888,0.0113,0.0543,0.3352</t>
-  </si>
-  <si>
-    <t>0.5979,0.0252,0.0500,0.3694</t>
-  </si>
-  <si>
-    <t>0.4924,0.0104,0.0097,0.5846</t>
-  </si>
-  <si>
-    <t>0.6752,0.0314,0.0697,0.2202</t>
-  </si>
-  <si>
-    <t>0.5940,0.0186,0.0217,0.4492</t>
-  </si>
-  <si>
-    <t>0.5122,0.0505,0.0501,0.3601</t>
-  </si>
-  <si>
-    <t>0.5300,0.0414,0.1124,0.3415</t>
-  </si>
-  <si>
-    <t>0.6474,0.0209,0.0434,0.2920</t>
-  </si>
-  <si>
-    <t>0.5277,0.0219,0.0674,0.4899</t>
-  </si>
-  <si>
-    <t>0.7929,0.0180,0.2009,0.0164</t>
-  </si>
-  <si>
-    <t>0.1306,0.1684,0.8325,0.0076</t>
-  </si>
-  <si>
-    <t>0.2086,0.0847,0.8110,0.0028</t>
-  </si>
-  <si>
-    <t>0.6441,0.0293,0.4360,0.0076</t>
-  </si>
-  <si>
-    <t>0.7434,0.0379,0.1668,0.0413</t>
-  </si>
-  <si>
-    <t>0.6313,0.2073,0.1603,0.0221</t>
-  </si>
-  <si>
-    <t>0.3908,0.4518,0.2633,0.0178</t>
-  </si>
-  <si>
-    <t>0.7565,0.0971,0.1470,0.0411</t>
-  </si>
-  <si>
-    <t>0.6359,0.1682,0.2019,0.0223</t>
-  </si>
-  <si>
-    <t>0.3676,0.4622,0.2846,0.0092</t>
-  </si>
-  <si>
-    <t>0.7109,0.0148,0.3122,0.0151</t>
-  </si>
-  <si>
-    <t>0.7781,0.0172,0.1515,0.0304</t>
-  </si>
-  <si>
-    <t>0.2933,0.0261,0.8470,0.0019</t>
-  </si>
-  <si>
-    <t>0.6337,0.0270,0.4506,0.0181</t>
-  </si>
-  <si>
-    <t>0.4210,0.0346,0.6368,0.0095</t>
-  </si>
-  <si>
-    <t>0.4185,0.0201,0.6689,0.0083</t>
-  </si>
-  <si>
-    <t>0.0039,0.0268,0.9939,0.0016</t>
-  </si>
-  <si>
-    <t>0.8092,0.0442,0.1579,0.0218</t>
-  </si>
-  <si>
-    <t>0.7326,0.0293,0.2147,0.0457</t>
-  </si>
-  <si>
-    <t>0.0076,0.0979,0.9834,0.0088</t>
-  </si>
-  <si>
-    <t>0.3989,0.2300,0.4551,0.0143</t>
-  </si>
-  <si>
-    <t>0.5632,0.0173,0.1349,0.1758</t>
-  </si>
-  <si>
-    <t>0.7308,0.0566,0.1371,0.0840</t>
-  </si>
-  <si>
-    <t>0.6121,0.0600,0.0886,0.1783</t>
-  </si>
-  <si>
-    <t>0.4463,0.3459,0.3110,0.0141</t>
-  </si>
-  <si>
-    <t>0.0228,0.4300,0.9347,0.0019</t>
-  </si>
-  <si>
-    <t>0.0520,0.0321,0.9640,0.0022</t>
-  </si>
-  <si>
-    <t>0.1172,0.0518,0.9309,0.0025</t>
-  </si>
-  <si>
-    <t>0.2564,0.0832,0.8011,0.0081</t>
-  </si>
-  <si>
-    <t>0.1419,0.1936,0.8739,0.0021</t>
-  </si>
-  <si>
-    <t>0.0718,0.5223,0.7964,0.0029</t>
-  </si>
-  <si>
-    <t>0.2197,0.1468,0.8091,0.0044</t>
-  </si>
-  <si>
-    <t>0.4900,0.1304,0.3585,0.1192</t>
-  </si>
-  <si>
-    <t>0.2802,0.5628,0.2539,0.0248</t>
-  </si>
-  <si>
-    <t>0.1658,0.7711,0.2108,0.0034</t>
-  </si>
-  <si>
-    <t>0.2678,0.5956,0.2600,0.0056</t>
-  </si>
-  <si>
-    <t>0.0112,0.1671,0.9804,0.0005</t>
-  </si>
-  <si>
-    <t>0.0135,0.2279,0.9723,0.0005</t>
-  </si>
-  <si>
-    <t>0.1786,0.0217,0.8959,0.0026</t>
-  </si>
-  <si>
-    <t>0.2361,0.1359,0.7411,0.0069</t>
-  </si>
-  <si>
-    <t>0.0070,0.2447,0.9789,0.0008</t>
-  </si>
-  <si>
-    <t>0.0459,0.3602,0.9118,0.0027</t>
-  </si>
-  <si>
-    <t>0.5220,0.0220,0.0514,0.3997</t>
-  </si>
-  <si>
-    <t>0.7574,0.0538,0.1032,0.0835</t>
-  </si>
-  <si>
-    <t>0.6420,0.0398,0.0566,0.2488</t>
-  </si>
-  <si>
-    <t>0.0842,0.5736,0.7550,0.0109</t>
-  </si>
-  <si>
-    <t>0.6315,0.0156,0.0380,0.3826</t>
-  </si>
-  <si>
-    <t>0.6335,0.0724,0.0652,0.1649</t>
-  </si>
-  <si>
-    <t>0.7685,0.0188,0.0240,0.2134</t>
-  </si>
-  <si>
-    <t>0.0206,0.5276,0.9472,0.0010</t>
-  </si>
-  <si>
-    <t>0.0133,0.2393,0.9823,0.0004</t>
-  </si>
-  <si>
-    <t>0.0350,0.0476,0.9650,0.0016</t>
-  </si>
-  <si>
-    <t>0.0019,0.9470,0.9514,0.0005</t>
-  </si>
-  <si>
-    <t>0.0613,0.0516,0.9548,0.0009</t>
-  </si>
-  <si>
-    <t>0.3558,0.4416,0.3101,0.0072</t>
-  </si>
-  <si>
-    <t>0.0723,0.8800,0.2216,0.0023</t>
-  </si>
-  <si>
-    <t>0.7396,0.0217,0.1854,0.0396</t>
-  </si>
-  <si>
-    <t>0.6850,0.0552,0.2553,0.0356</t>
-  </si>
-  <si>
-    <t>0.4245,0.1024,0.6609,0.0094</t>
-  </si>
-  <si>
-    <t>0.0027,0.8902,0.9643,0.0004</t>
-  </si>
-  <si>
-    <t>0.0547,0.3692,0.8933,0.0016</t>
-  </si>
-  <si>
-    <t>0.0039,0.8939,0.9399,0.0006</t>
-  </si>
-  <si>
-    <t>0.0038,0.8828,0.9551,0.0005</t>
-  </si>
-  <si>
-    <t>0.5000,0.0125,0.1586,0.2330</t>
-  </si>
-  <si>
-    <t>0.4769,0.0077,0.0441,0.4787</t>
-  </si>
-  <si>
-    <t>0.2709,0.0026,0.0456,0.6298</t>
-  </si>
-  <si>
-    <t>0.3219,0.0067,0.1695,0.3626</t>
-  </si>
-  <si>
-    <t>0.5285,0.0063,0.1194,0.1959</t>
-  </si>
-  <si>
-    <t>0.7139,0.0023,0.0170,0.2055</t>
-  </si>
-  <si>
-    <t>0.0192,0.6911,0.9318,0.0013</t>
-  </si>
-  <si>
-    <t>0.0027,0.5825,0.9901,0.0002</t>
-  </si>
-  <si>
-    <t>0.0045,0.4227,0.9862,0.0002</t>
-  </si>
-  <si>
-    <t>0.0245,0.2506,0.9524,0.0009</t>
-  </si>
-  <si>
-    <t>0.0072,0.5636,0.9771,0.0004</t>
-  </si>
-  <si>
-    <t>0.0175,0.7442,0.9125,0.0017</t>
-  </si>
-  <si>
-    <t>0.7476,0.0093,0.0084,0.3092</t>
-  </si>
-  <si>
-    <t>0.6301,0.0385,0.0449,0.2582</t>
-  </si>
-  <si>
-    <t>0.8275,0.0348,0.0652,0.0501</t>
-  </si>
-  <si>
-    <t>0.4902,0.0245,0.0695,0.4440</t>
-  </si>
-  <si>
-    <t>0.6361,0.0358,0.0917,0.2426</t>
-  </si>
-  <si>
-    <t>0.5295,0.0377,0.0850,0.3889</t>
-  </si>
-  <si>
-    <t>0.6577,0.0302,0.0404,0.2521</t>
-  </si>
-  <si>
-    <t>0.8185,0.0275,0.0395,0.0712</t>
-  </si>
-  <si>
-    <t>0.5897,0.0113,0.0237,0.4818</t>
-  </si>
-  <si>
-    <t>0.6946,0.0218,0.0333,0.2631</t>
-  </si>
-  <si>
-    <t>0.7139,0.0558,0.0281,0.1465</t>
-  </si>
-  <si>
-    <t>0.5729,0.0156,0.0280,0.4934</t>
-  </si>
-  <si>
-    <t>0.4752,0.0096,0.0297,0.5882</t>
-  </si>
-  <si>
-    <t>0.6024,0.0234,0.0409,0.3256</t>
-  </si>
-  <si>
-    <t>0.6148,0.0150,0.0247,0.4245</t>
-  </si>
-  <si>
-    <t>0.7556,0.0067,0.0308,0.2298</t>
-  </si>
-  <si>
-    <t>0.0171,0.0057,0.9795,0.0053</t>
-  </si>
-  <si>
-    <t>0.4366,0.0562,0.6544,0.0078</t>
-  </si>
-  <si>
-    <t>0.7618,0.0240,0.2386,0.0184</t>
-  </si>
-  <si>
-    <t>0.0660,0.0456,0.9359,0.0045</t>
-  </si>
-  <si>
-    <t>0.4525,0.2612,0.2765,0.0666</t>
-  </si>
-  <si>
-    <t>0.7053,0.0721,0.1671,0.0417</t>
-  </si>
-  <si>
-    <t>0.4972,0.3141,0.1203,0.0535</t>
-  </si>
-  <si>
-    <t>0.5070,0.2699,0.2812,0.0647</t>
-  </si>
-  <si>
-    <t>0.4195,0.2781,0.3393,0.0682</t>
-  </si>
-  <si>
-    <t>0.1383,0.7957,0.1876,0.0145</t>
-  </si>
-  <si>
-    <t>0.5685,0.0438,0.1539,0.1917</t>
-  </si>
-  <si>
-    <t>0.5959,0.0375,0.2631,0.0786</t>
-  </si>
-  <si>
-    <t>0.3163,0.0366,0.6744,0.0298</t>
-  </si>
-  <si>
-    <t>0.7402,0.0417,0.2908,0.0147</t>
-  </si>
-  <si>
-    <t>0.5325,0.2172,0.2561,0.0730</t>
-  </si>
-  <si>
-    <t>0.2831,0.0163,0.1580,0.5028</t>
-  </si>
-  <si>
-    <t>0.6317,0.2305,0.1045,0.0038</t>
-  </si>
-  <si>
-    <t>0.7114,0.1311,0.1333,0.0084</t>
-  </si>
-  <si>
-    <t>0.6760,0.0603,0.2682,0.0357</t>
-  </si>
-  <si>
-    <t>0.0418,0.8660,0.5930,0.0012</t>
-  </si>
-  <si>
-    <t>0.8361,0.0553,0.0972,0.0159</t>
-  </si>
-  <si>
-    <t>0.5824,0.0826,0.1613,0.1127</t>
-  </si>
-  <si>
-    <t>0.4466,0.1850,0.1628,0.1353</t>
-  </si>
-  <si>
-    <t>0.7989,0.0602,0.0859,0.0677</t>
-  </si>
-  <si>
-    <t>0.5132,0.0160,0.0707,0.4543</t>
-  </si>
-  <si>
-    <t>0.7544,0.0289,0.0304,0.1411</t>
-  </si>
-  <si>
-    <t>0.6875,0.0191,0.0294,0.2376</t>
-  </si>
-  <si>
-    <t>0.6368,0.0508,0.0409,0.1586</t>
-  </si>
-  <si>
-    <t>0.8839,0.0200,0.0399,0.0412</t>
-  </si>
-  <si>
-    <t>0.7230,0.0124,0.0294,0.2585</t>
-  </si>
-  <si>
-    <t>0.6791,0.0524,0.1632,0.1093</t>
-  </si>
-  <si>
-    <t>0.0100,0.5711,0.9792,0.0006</t>
-  </si>
-  <si>
-    <t>0.0600,0.4401,0.8568,0.0012</t>
-  </si>
-  <si>
-    <t>0.0056,0.1728,0.9906,0.0004</t>
-  </si>
-  <si>
-    <t>0.1864,0.0400,0.8962,0.0013</t>
-  </si>
-  <si>
-    <t>0.7496,0.0569,0.1642,0.0346</t>
-  </si>
-  <si>
-    <t>0.7268,0.0423,0.2609,0.0278</t>
-  </si>
-  <si>
-    <t>0.7098,0.0264,0.2766,0.0410</t>
-  </si>
-  <si>
-    <t>0.7650,0.0219,0.1642,0.0310</t>
-  </si>
-  <si>
-    <t>0.5374,0.0036,0.0548,0.3484</t>
-  </si>
-  <si>
-    <t>0.1261,0.0036,0.0380,0.8487</t>
-  </si>
-  <si>
-    <t>0.1972,0.0044,0.0361,0.7601</t>
-  </si>
-  <si>
-    <t>0.4992,0.0035,0.0993,0.2327</t>
-  </si>
-  <si>
-    <t>0.0206,0.7994,0.7687,0.0018</t>
-  </si>
-  <si>
-    <t>0.7089,0.0147,0.0777,0.1382</t>
-  </si>
-  <si>
-    <t>0.6381,0.1958,0.2170,0.0321</t>
-  </si>
-  <si>
-    <t>0.5478,0.0474,0.0598,0.3108</t>
-  </si>
-  <si>
-    <t>0.6211,0.0270,0.0692,0.3018</t>
-  </si>
-  <si>
-    <t>0.5954,0.0252,0.0519,0.3259</t>
-  </si>
-  <si>
-    <t>0.7591,0.0083,0.0617,0.0995</t>
-  </si>
-  <si>
-    <t>0.5133,0.0149,0.1151,0.3684</t>
-  </si>
-  <si>
-    <t>0.0701,0.0283,0.9423,0.0091</t>
-  </si>
-  <si>
-    <t>0.3019,0.0202,0.1348,0.6280</t>
-  </si>
-  <si>
-    <t>0.5174,0.0252,0.0749,0.4056</t>
-  </si>
-  <si>
-    <t>0.7361,0.0567,0.2311,0.0329</t>
-  </si>
-  <si>
-    <t>0.8518,0.0141,0.1111,0.0189</t>
-  </si>
-  <si>
-    <t>0.7297,0.0236,0.2349,0.0377</t>
-  </si>
-  <si>
-    <t>0.4452,0.3396,0.2607,0.0355</t>
-  </si>
-  <si>
-    <t>0.7176,0.0558,0.2054,0.0417</t>
-  </si>
-  <si>
-    <t>0.8212,0.0306,0.1223,0.0221</t>
-  </si>
-  <si>
-    <t>0.6866,0.0146,0.0244,0.3177</t>
-  </si>
-  <si>
-    <t>0.4782,0.0170,0.0460,0.5717</t>
-  </si>
-  <si>
-    <t>0.7219,0.0193,0.0324,0.1949</t>
-  </si>
-  <si>
-    <t>0.3348,0.0237,0.0537,0.6666</t>
-  </si>
-  <si>
-    <t>0.6521,0.0076,0.0261,0.3599</t>
-  </si>
-  <si>
-    <t>0.5973,0.0928,0.0916,0.1891</t>
-  </si>
-  <si>
-    <t>0.5265,0.0658,0.0512,0.2799</t>
-  </si>
-  <si>
-    <t>0.4919,0.0522,0.0495,0.3602</t>
-  </si>
-  <si>
-    <t>0.7769,0.0398,0.1553,0.0349</t>
-  </si>
-  <si>
-    <t>0.7094,0.1102,0.1041,0.0488</t>
-  </si>
-  <si>
-    <t>0.6806,0.0845,0.1363,0.0593</t>
-  </si>
-  <si>
-    <t>0.4651,0.1094,0.4328,0.1583</t>
-  </si>
-  <si>
-    <t>0.7803,0.0177,0.0914,0.0857</t>
-  </si>
-  <si>
-    <t>0.8415,0.0351,0.0492,0.0481</t>
-  </si>
-  <si>
-    <t>0.6036,0.0333,0.0719,0.2503</t>
-  </si>
-  <si>
-    <t>0.7496,0.0179,0.0771,0.1031</t>
-  </si>
-  <si>
-    <t>0.0174,0.1635,0.9688,0.0048</t>
-  </si>
-  <si>
-    <t>0.5833,0.0896,0.1775,0.1603</t>
-  </si>
-  <si>
-    <t>0.0299,0.0520,0.9861,0.0011</t>
-  </si>
-  <si>
-    <t>0.0452,0.2346,0.9478,0.0011</t>
-  </si>
-  <si>
-    <t>0.1249,0.0638,0.8737,0.0125</t>
-  </si>
-  <si>
-    <t>0.0363,0.4166,0.9304,0.0013</t>
-  </si>
-  <si>
-    <t>0.7618,0.0252,0.2885,0.0051</t>
-  </si>
-  <si>
-    <t>0.0202,0.0455,0.9803,0.0014</t>
-  </si>
-  <si>
-    <t>0.1403,0.0664,0.8983,0.0029</t>
-  </si>
-  <si>
-    <t>0.7632,0.0354,0.2577,0.0170</t>
-  </si>
-  <si>
-    <t>0.6923,0.0599,0.3455,0.0168</t>
-  </si>
-  <si>
-    <t>0.7558,0.0372,0.2960,0.0097</t>
-  </si>
-  <si>
-    <t>0.5351,0.0538,0.5427,0.0169</t>
-  </si>
-  <si>
-    <t>0.6781,0.0481,0.3674,0.0131</t>
-  </si>
-  <si>
-    <t>0.6554,0.1027,0.3043,0.0128</t>
-  </si>
-  <si>
-    <t>0.3412,0.1356,0.5275,0.0693</t>
-  </si>
-  <si>
-    <t>0.6155,0.0433,0.4623,0.0164</t>
-  </si>
-  <si>
-    <t>0.7328,0.1055,0.0811,0.0688</t>
-  </si>
-  <si>
-    <t>0.6996,0.1506,0.0661,0.0372</t>
-  </si>
-  <si>
-    <t>0.6869,0.1728,0.0947,0.0415</t>
-  </si>
-  <si>
-    <t>0.6488,0.1005,0.0963,0.1116</t>
-  </si>
-  <si>
-    <t>0.6027,0.1168,0.0700,0.0992</t>
-  </si>
-  <si>
-    <t>0.9007,0.0133,0.0748,0.0082</t>
-  </si>
-  <si>
-    <t>0.7035,0.0302,0.2609,0.0329</t>
-  </si>
-  <si>
-    <t>0.7905,0.0332,0.2434,0.0070</t>
-  </si>
-  <si>
-    <t>0.4185,0.0765,0.5799,0.0390</t>
-  </si>
-  <si>
-    <t>0.7835,0.0139,0.2209,0.0178</t>
-  </si>
-  <si>
-    <t>0.6032,0.0351,0.4013,0.0403</t>
-  </si>
-  <si>
-    <t>0.0702,0.4106,0.8222,0.0055</t>
-  </si>
-  <si>
-    <t>0.2315,0.0963,0.8584,0.0022</t>
-  </si>
-  <si>
-    <t>0.1996,0.0329,0.8776,0.0034</t>
-  </si>
-  <si>
-    <t>0.0626,0.1102,0.9469,0.0019</t>
-  </si>
-  <si>
-    <t>0.2746,0.0436,0.0752,0.6338</t>
-  </si>
-  <si>
-    <t>0.5424,0.0586,0.1709,0.2732</t>
-  </si>
-  <si>
-    <t>0.5093,0.0337,0.0719,0.4041</t>
-  </si>
-  <si>
-    <t>0.5304,0.0296,0.0763,0.3714</t>
-  </si>
-  <si>
-    <t>0.6841,0.0200,0.0565,0.2492</t>
-  </si>
-  <si>
-    <t>0.6818,0.0353,0.0443,0.2307</t>
-  </si>
-  <si>
-    <t>0.6895,0.0309,0.0369,0.2070</t>
-  </si>
-  <si>
-    <t>0.8233,0.0060,0.0176,0.1625</t>
-  </si>
-  <si>
-    <t>0.1500,0.1916,0.7939,0.0120</t>
-  </si>
-  <si>
-    <t>0.6828,0.0564,0.2427,0.0453</t>
-  </si>
-  <si>
-    <t>0.8034,0.0148,0.1154,0.0414</t>
-  </si>
-  <si>
-    <t>0.0404,0.0642,0.9605,0.0033</t>
-  </si>
-  <si>
-    <t>0.0036,0.0827,0.9907,0.0011</t>
-  </si>
-  <si>
-    <t>0.3121,0.0773,0.7889,0.0044</t>
-  </si>
-  <si>
-    <t>0.0038,0.0393,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.5756,0.0472,0.4959,0.0102</t>
-  </si>
-  <si>
-    <t>0.0154,0.0179,0.9898,0.0004</t>
-  </si>
-  <si>
-    <t>0.0372,0.0316,0.9701,0.0016</t>
-  </si>
-  <si>
-    <t>0.4621,0.1887,0.4654,0.0293</t>
-  </si>
-  <si>
-    <t>0.6707,0.0206,0.3470,0.0179</t>
-  </si>
-  <si>
-    <t>0.6911,0.0468,0.3416,0.0238</t>
-  </si>
-  <si>
-    <t>0.6069,0.0098,0.3464,0.0277</t>
-  </si>
-  <si>
-    <t>0.7905,0.0232,0.0166,0.1223</t>
-  </si>
-  <si>
-    <t>0.7244,0.0285,0.0246,0.2084</t>
-  </si>
-  <si>
-    <t>0.5058,0.0067,0.0113,0.6720</t>
-  </si>
-  <si>
-    <t>0.6806,0.0171,0.0262,0.2607</t>
-  </si>
-  <si>
-    <t>0.7876,0.0276,0.0317,0.1036</t>
-  </si>
-  <si>
-    <t>0.7321,0.0280,0.0343,0.1895</t>
-  </si>
-  <si>
-    <t>0.7454,0.0200,0.0325,0.1848</t>
-  </si>
-  <si>
-    <t>0.7692,0.0236,0.0346,0.1647</t>
-  </si>
-  <si>
-    <t>0.2627,0.0777,0.8102,0.0046</t>
-  </si>
-  <si>
-    <t>0.0496,0.2259,0.9545,0.0024</t>
-  </si>
-  <si>
-    <t>0.0632,0.1016,0.9541,0.0006</t>
-  </si>
-  <si>
-    <t>0.2523,0.1849,0.6899,0.0051</t>
-  </si>
-  <si>
-    <t>0.0458,0.0689,0.9695,0.0008</t>
-  </si>
-  <si>
-    <t>0.5851,0.0102,0.2386,0.0645</t>
-  </si>
-  <si>
-    <t>0.4261,0.0533,0.6305,0.0166</t>
-  </si>
-  <si>
-    <t>0.2492,0.0206,0.8712,0.0025</t>
-  </si>
-  <si>
-    <t>0.6311,0.0124,0.0723,0.1915</t>
-  </si>
-  <si>
-    <t>0.4619,0.0046,0.1801,0.1313</t>
-  </si>
-  <si>
-    <t>0.4766,0.0029,0.0586,0.3009</t>
-  </si>
-  <si>
-    <t>0.1188,0.0005,0.0218,0.8396</t>
-  </si>
-  <si>
-    <t>0.1973,0.0009,0.0142,0.7730</t>
-  </si>
-  <si>
-    <t>0.4052,0.0890,0.4649,0.1194</t>
+    <t>0.1265,0.0351,0.0260,0.8884</t>
+  </si>
+  <si>
+    <t>0.0126,0.0256,0.0006,0.9884</t>
+  </si>
+  <si>
+    <t>0.1938,0.2848,0.0058,0.4215</t>
+  </si>
+  <si>
+    <t>0.0224,0.0084,0.0015,0.9880</t>
+  </si>
+  <si>
+    <t>0.9938,0.0057,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9821,0.0211,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9887,0.0102,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.9942,0.0036,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9860,0.0159,0.0011,0.0020</t>
+  </si>
+  <si>
+    <t>0.9868,0.0158,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9889,0.0120,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9895,0.0105,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.7810,0.0850,0.1393,0.0188</t>
+  </si>
+  <si>
+    <t>0.1181,0.1746,0.7771,0.0097</t>
+  </si>
+  <si>
+    <t>0.1695,0.0565,0.8251,0.0024</t>
+  </si>
+  <si>
+    <t>0.0939,0.0654,0.8601,0.0019</t>
+  </si>
+  <si>
+    <t>0.6204,0.1323,0.0923,0.1092</t>
+  </si>
+  <si>
+    <t>0.0012,0.9941,0.0034,0.0027</t>
+  </si>
+  <si>
+    <t>0.0031,0.9923,0.0069,0.0016</t>
+  </si>
+  <si>
+    <t>0.2288,0.8135,0.0323,0.0031</t>
+  </si>
+  <si>
+    <t>0.0205,0.9715,0.0067,0.0035</t>
+  </si>
+  <si>
+    <t>0.0041,0.9924,0.0035,0.0008</t>
+  </si>
+  <si>
+    <t>0.2275,0.0923,0.7020,0.0222</t>
+  </si>
+  <si>
+    <t>0.0733,0.6259,0.6383,0.0123</t>
+  </si>
+  <si>
+    <t>0.0119,0.0068,0.9855,0.0018</t>
+  </si>
+  <si>
+    <t>0.0275,0.0149,0.9442,0.0113</t>
+  </si>
+  <si>
+    <t>0.0185,0.0156,0.9594,0.0105</t>
+  </si>
+  <si>
+    <t>0.0169,0.0024,0.9801,0.0024</t>
+  </si>
+  <si>
+    <t>0.0011,0.0014,0.9979,0.0011</t>
+  </si>
+  <si>
+    <t>0.1441,0.7704,0.1310,0.0041</t>
+  </si>
+  <si>
+    <t>0.1036,0.7955,0.1378,0.0060</t>
+  </si>
+  <si>
+    <t>0.0019,0.0122,0.9951,0.0057</t>
+  </si>
+  <si>
+    <t>0.0082,0.9272,0.2497,0.0017</t>
+  </si>
+  <si>
+    <t>0.2225,0.7567,0.0624,0.0171</t>
+  </si>
+  <si>
+    <t>0.0624,0.0626,0.8411,0.0748</t>
+  </si>
+  <si>
+    <t>0.7453,0.4004,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.0404,0.9363,0.1298,0.0044</t>
+  </si>
+  <si>
+    <t>0.0099,0.9339,0.1543,0.0045</t>
+  </si>
+  <si>
+    <t>0.0106,0.5071,0.9376,0.0109</t>
+  </si>
+  <si>
+    <t>0.0642,0.3239,0.8488,0.0058</t>
+  </si>
+  <si>
+    <t>0.0036,0.0110,0.9914,0.0058</t>
+  </si>
+  <si>
+    <t>0.0027,0.6876,0.9743,0.0004</t>
+  </si>
+  <si>
+    <t>0.0037,0.9845,0.0110,0.0007</t>
+  </si>
+  <si>
+    <t>0.0064,0.2613,0.9769,0.0010</t>
+  </si>
+  <si>
+    <t>0.0565,0.2579,0.0104,0.8167</t>
+  </si>
+  <si>
+    <t>0.0017,0.9887,0.0038,0.0086</t>
+  </si>
+  <si>
+    <t>0.0011,0.9960,0.0074,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9956,0.0429,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.6762,0.8988,0.0031</t>
+  </si>
+  <si>
+    <t>0.0059,0.5024,0.9662,0.0012</t>
+  </si>
+  <si>
+    <t>0.0226,0.0272,0.9608,0.0062</t>
+  </si>
+  <si>
+    <t>0.0510,0.0062,0.9514,0.0049</t>
+  </si>
+  <si>
+    <t>0.0040,0.0182,0.9867,0.0031</t>
+  </si>
+  <si>
+    <t>0.0066,0.0454,0.9763,0.0031</t>
+  </si>
+  <si>
+    <t>0.9328,0.1026,0.0023,0.0027</t>
+  </si>
+  <si>
+    <t>0.9818,0.0140,0.0051,0.0010</t>
+  </si>
+  <si>
+    <t>0.9112,0.1225,0.0023,0.0042</t>
+  </si>
+  <si>
+    <t>0.0271,0.1336,0.9521,0.0244</t>
+  </si>
+  <si>
+    <t>0.9701,0.0316,0.0060,0.0021</t>
+  </si>
+  <si>
+    <t>0.9768,0.0237,0.0044,0.0013</t>
+  </si>
+  <si>
+    <t>0.9123,0.1194,0.0067,0.0035</t>
+  </si>
+  <si>
+    <t>0.0006,0.9782,0.8401,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.4876,0.9880,0.0011</t>
+  </si>
+  <si>
+    <t>0.0033,0.1861,0.9819,0.0027</t>
+  </si>
+  <si>
+    <t>0.0002,0.9631,0.9836,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.0110,0.9941,0.0008</t>
+  </si>
+  <si>
+    <t>0.0084,0.9801,0.0277,0.0009</t>
+  </si>
+  <si>
+    <t>0.0099,0.9837,0.0044,0.0012</t>
+  </si>
+  <si>
+    <t>0.8128,0.0492,0.1276,0.0431</t>
+  </si>
+  <si>
+    <t>0.5176,0.1570,0.4424,0.0224</t>
+  </si>
+  <si>
+    <t>0.0064,0.0164,0.9866,0.0077</t>
+  </si>
+  <si>
+    <t>0.0001,0.9816,0.9833,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9541,0.8843,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.9902,0.7960,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9794,0.9469,0.0001</t>
+  </si>
+  <si>
+    <t>0.0058,0.0028,0.0055,0.9935</t>
+  </si>
+  <si>
+    <t>0.0010,0.0502,0.0005,0.9966</t>
+  </si>
+  <si>
+    <t>0.0027,0.0136,0.0003,0.9972</t>
+  </si>
+  <si>
+    <t>0.0023,0.0021,0.0005,0.9983</t>
+  </si>
+  <si>
+    <t>0.0006,0.0077,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0008,0.0100,0.0004,0.9984</t>
+  </si>
+  <si>
+    <t>0.0002,0.9928,0.8925,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.7795,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.6733,0.9348,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9616,0.9365,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9552,0.8670,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9219,0.9505,0.0004</t>
+  </si>
+  <si>
+    <t>0.9935,0.0057,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9352,0.0766,0.0082,0.0036</t>
+  </si>
+  <si>
+    <t>0.9602,0.0647,0.0023,0.0022</t>
+  </si>
+  <si>
+    <t>0.9704,0.0195,0.0007,0.0055</t>
+  </si>
+  <si>
+    <t>0.9768,0.0263,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9937,0.0079,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9098,0.1050,0.0128,0.0036</t>
+  </si>
+  <si>
+    <t>0.9926,0.0094,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9885,0.0138,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.9857,0.0125,0.0026,0.0029</t>
+  </si>
+  <si>
+    <t>0.9958,0.0053,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0097,0.0027,0.0022</t>
+  </si>
+  <si>
+    <t>0.9799,0.0232,0.0006,0.0023</t>
+  </si>
+  <si>
+    <t>0.9240,0.1405,0.0032,0.0012</t>
+  </si>
+  <si>
+    <t>0.9896,0.0082,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.9925,0.0071,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0077,0.0050,0.9917,0.0019</t>
+  </si>
+  <si>
+    <t>0.0117,0.0917,0.9698,0.0013</t>
+  </si>
+  <si>
+    <t>0.5946,0.0378,0.4326,0.0395</t>
+  </si>
+  <si>
+    <t>0.0237,0.0060,0.9684,0.0039</t>
+  </si>
+  <si>
+    <t>0.0576,0.9510,0.0033,0.0021</t>
+  </si>
+  <si>
+    <t>0.0065,0.9908,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.1014,0.9100,0.0115,0.0064</t>
+  </si>
+  <si>
+    <t>0.2697,0.7718,0.0204,0.0047</t>
+  </si>
+  <si>
+    <t>0.0115,0.9750,0.0057,0.0048</t>
+  </si>
+  <si>
+    <t>0.0071,0.9856,0.0035,0.0013</t>
+  </si>
+  <si>
+    <t>0.5916,0.5766,0.0053,0.0011</t>
+  </si>
+  <si>
+    <t>0.0914,0.1114,0.1857,0.7022</t>
+  </si>
+  <si>
+    <t>0.1578,0.0170,0.8530,0.0051</t>
+  </si>
+  <si>
+    <t>0.6359,0.0683,0.2557,0.0746</t>
+  </si>
+  <si>
+    <t>0.1087,0.8208,0.0725,0.0208</t>
+  </si>
+  <si>
+    <t>0.0197,0.0536,0.0515,0.9429</t>
+  </si>
+  <si>
+    <t>0.0011,0.9962,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.0044,0.9859,0.0126,0.0044</t>
+  </si>
+  <si>
+    <t>0.0001,0.9981,0.0038,0.0014</t>
+  </si>
+  <si>
+    <t>0.0010,0.9939,0.1749,0.0004</t>
+  </si>
+  <si>
+    <t>0.0186,0.9649,0.0591,0.0029</t>
+  </si>
+  <si>
+    <t>0.5651,0.5659,0.0097,0.0048</t>
+  </si>
+  <si>
+    <t>0.2527,0.8097,0.0142,0.0042</t>
+  </si>
+  <si>
+    <t>0.9753,0.0228,0.0024,0.0031</t>
+  </si>
+  <si>
+    <t>0.9876,0.0098,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9607,0.0236,0.0054,0.0126</t>
+  </si>
+  <si>
+    <t>0.9202,0.0903,0.0131,0.0032</t>
+  </si>
+  <si>
+    <t>0.9843,0.0132,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.9171,0.0911,0.0116,0.0025</t>
+  </si>
+  <si>
+    <t>0.9333,0.0923,0.0049,0.0028</t>
+  </si>
+  <si>
+    <t>0.9753,0.0179,0.0061,0.0044</t>
+  </si>
+  <si>
+    <t>0.0004,0.9378,0.9869,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.8600,0.9413,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.6036,0.9829,0.0011</t>
+  </si>
+  <si>
+    <t>0.0043,0.6179,0.9439,0.0009</t>
+  </si>
+  <si>
+    <t>0.7515,0.0729,0.1396,0.0332</t>
+  </si>
+  <si>
+    <t>0.5614,0.1438,0.3115,0.0670</t>
+  </si>
+  <si>
+    <t>0.2168,0.0209,0.8534,0.0120</t>
+  </si>
+  <si>
+    <t>0.5266,0.1318,0.1229,0.1171</t>
+  </si>
+  <si>
+    <t>0.0304,0.0045,0.0011,0.9877</t>
+  </si>
+  <si>
+    <t>0.0001,0.0060,0.0007,0.9994</t>
+  </si>
+  <si>
+    <t>0.0029,0.0148,0.0008,0.9961</t>
+  </si>
+  <si>
+    <t>0.0044,0.0017,0.0010,0.9969</t>
+  </si>
+  <si>
+    <t>0.0014,0.9815,0.4562,0.0008</t>
+  </si>
+  <si>
+    <t>0.9919,0.0040,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.0145,0.9774,0.0084,0.0020</t>
+  </si>
+  <si>
+    <t>0.9459,0.0441,0.0068,0.0130</t>
+  </si>
+  <si>
+    <t>0.3004,0.7110,0.0241,0.0173</t>
+  </si>
+  <si>
+    <t>0.9501,0.0212,0.0127,0.0160</t>
+  </si>
+  <si>
+    <t>0.0827,0.0386,0.0014,0.9026</t>
+  </si>
+  <si>
+    <t>0.9734,0.0262,0.0044,0.0032</t>
+  </si>
+  <si>
+    <t>0.0667,0.0912,0.8929,0.0635</t>
+  </si>
+  <si>
+    <t>0.8632,0.0242,0.0069,0.0926</t>
+  </si>
+  <si>
+    <t>0.6069,0.0576,0.0021,0.1820</t>
+  </si>
+  <si>
+    <t>0.2592,0.6175,0.0034,0.0354</t>
+  </si>
+  <si>
+    <t>0.6881,0.2199,0.1188,0.0255</t>
+  </si>
+  <si>
+    <t>0.8064,0.1420,0.0355,0.0134</t>
+  </si>
+  <si>
+    <t>0.0501,0.8952,0.0192,0.0456</t>
+  </si>
+  <si>
+    <t>0.2090,0.7496,0.0608,0.0219</t>
+  </si>
+  <si>
+    <t>0.2168,0.7646,0.0740,0.0176</t>
+  </si>
+  <si>
+    <t>0.9786,0.0160,0.0049,0.0038</t>
+  </si>
+  <si>
+    <t>0.9573,0.0592,0.0033,0.0034</t>
+  </si>
+  <si>
+    <t>0.9898,0.0098,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9741,0.0085,0.0034,0.0114</t>
+  </si>
+  <si>
+    <t>0.9829,0.0131,0.0014,0.0032</t>
+  </si>
+  <si>
+    <t>0.9612,0.0423,0.0059,0.0027</t>
+  </si>
+  <si>
+    <t>0.9692,0.0317,0.0045,0.0046</t>
+  </si>
+  <si>
+    <t>0.9823,0.0118,0.0015,0.0048</t>
+  </si>
+  <si>
+    <t>0.6166,0.4360,0.0178,0.0076</t>
+  </si>
+  <si>
+    <t>0.5382,0.6025,0.0069,0.0033</t>
+  </si>
+  <si>
+    <t>0.4466,0.6898,0.0039,0.0022</t>
+  </si>
+  <si>
+    <t>0.1229,0.6337,0.4104,0.0267</t>
+  </si>
+  <si>
+    <t>0.9777,0.0309,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.8241,0.2229,0.0070,0.0075</t>
+  </si>
+  <si>
+    <t>0.9833,0.0164,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.8054,0.2167,0.0047,0.0100</t>
+  </si>
+  <si>
+    <t>0.0010,0.0186,0.9982,0.0010</t>
+  </si>
+  <si>
+    <t>0.9267,0.0702,0.0094,0.0110</t>
+  </si>
+  <si>
+    <t>0.0040,0.0210,0.9952,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.4606,0.9913,0.0015</t>
+  </si>
+  <si>
+    <t>0.0198,0.0171,0.9765,0.0074</t>
+  </si>
+  <si>
+    <t>0.0022,0.3537,0.9788,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.0202,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0013,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.0048,0.9903,0.0026</t>
+  </si>
+  <si>
+    <t>0.0993,0.1307,0.7022,0.1056</t>
+  </si>
+  <si>
+    <t>0.1565,0.1067,0.7710,0.0214</t>
+  </si>
+  <si>
+    <t>0.2805,0.1351,0.6496,0.0282</t>
+  </si>
+  <si>
+    <t>0.0174,0.8151,0.4336,0.0022</t>
+  </si>
+  <si>
+    <t>0.0706,0.7772,0.4150,0.0072</t>
+  </si>
+  <si>
+    <t>0.0072,0.9627,0.1429,0.0178</t>
+  </si>
+  <si>
+    <t>0.1084,0.7282,0.2096,0.0936</t>
+  </si>
+  <si>
+    <t>0.0560,0.6131,0.4287,0.0347</t>
+  </si>
+  <si>
+    <t>0.2129,0.8514,0.0082,0.0030</t>
+  </si>
+  <si>
+    <t>0.7229,0.3446,0.0045,0.0070</t>
+  </si>
+  <si>
+    <t>0.8365,0.2663,0.0024,0.0034</t>
+  </si>
+  <si>
+    <t>0.9505,0.0723,0.0030,0.0012</t>
+  </si>
+  <si>
+    <t>0.9248,0.1193,0.0035,0.0015</t>
+  </si>
+  <si>
+    <t>0.1183,0.7340,0.1698,0.0352</t>
+  </si>
+  <si>
+    <t>0.7928,0.0335,0.1673,0.0270</t>
+  </si>
+  <si>
+    <t>0.6833,0.0179,0.1845,0.0643</t>
+  </si>
+  <si>
+    <t>0.2070,0.0189,0.8090,0.0090</t>
+  </si>
+  <si>
+    <t>0.5313,0.1035,0.3866,0.0893</t>
+  </si>
+  <si>
+    <t>0.0178,0.0798,0.8441,0.1195</t>
+  </si>
+  <si>
+    <t>0.0036,0.7484,0.9463,0.0020</t>
+  </si>
+  <si>
+    <t>0.0125,0.3391,0.9633,0.0038</t>
+  </si>
+  <si>
+    <t>0.0191,0.3962,0.8864,0.0032</t>
+  </si>
+  <si>
+    <t>0.0020,0.3039,0.9856,0.0009</t>
+  </si>
+  <si>
+    <t>0.9841,0.0169,0.0013,0.0021</t>
+  </si>
+  <si>
+    <t>0.9733,0.0203,0.0047,0.0060</t>
+  </si>
+  <si>
+    <t>0.9730,0.0393,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.9816,0.0240,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.9815,0.0169,0.0016,0.0034</t>
+  </si>
+  <si>
+    <t>0.9850,0.0226,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9758,0.0203,0.0016,0.0056</t>
+  </si>
+  <si>
+    <t>0.9847,0.0115,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.0465,0.0297,0.9423,0.0079</t>
+  </si>
+  <si>
+    <t>0.1549,0.5906,0.3572,0.0261</t>
+  </si>
+  <si>
+    <t>0.8293,0.0499,0.1492,0.0135</t>
+  </si>
+  <si>
+    <t>0.0057,0.0131,0.9906,0.0014</t>
+  </si>
+  <si>
+    <t>0.0047,0.0039,0.9887,0.0040</t>
+  </si>
+  <si>
+    <t>0.0037,0.5106,0.9394,0.0012</t>
+  </si>
+  <si>
+    <t>0.0018,0.0194,0.9951,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.1773,0.9675,0.0015</t>
+  </si>
+  <si>
+    <t>0.0015,0.1007,0.9947,0.0013</t>
+  </si>
+  <si>
+    <t>0.0093,0.0847,0.9590,0.0040</t>
+  </si>
+  <si>
+    <t>0.0169,0.4439,0.6786,0.0201</t>
+  </si>
+  <si>
+    <t>0.6639,0.0685,0.3265,0.0354</t>
+  </si>
+  <si>
+    <t>0.5787,0.0796,0.4548,0.0132</t>
+  </si>
+  <si>
+    <t>0.5670,0.0238,0.3655,0.0650</t>
+  </si>
+  <si>
+    <t>0.9693,0.0453,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.9877,0.0157,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9903,0.0143,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9706,0.0265,0.0046,0.0042</t>
+  </si>
+  <si>
+    <t>0.9830,0.0105,0.0011,0.0053</t>
+  </si>
+  <si>
+    <t>0.9830,0.0233,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.9840,0.0214,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9843,0.0195,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.0203,0.3878,0.8757,0.0027</t>
+  </si>
+  <si>
+    <t>0.0043,0.0694,0.9804,0.0039</t>
+  </si>
+  <si>
+    <t>0.0119,0.1817,0.9680,0.0065</t>
+  </si>
+  <si>
+    <t>0.0429,0.3113,0.6969,0.0220</t>
+  </si>
+  <si>
+    <t>0.0067,0.0113,0.9840,0.0037</t>
+  </si>
+  <si>
+    <t>0.0107,0.0102,0.9515,0.1213</t>
+  </si>
+  <si>
+    <t>0.0839,0.1646,0.8125,0.0177</t>
+  </si>
+  <si>
+    <t>0.0150,0.0161,0.6079,0.4786</t>
+  </si>
+  <si>
+    <t>0.3817,0.0141,0.0049,0.7259</t>
+  </si>
+  <si>
+    <t>0.0013,0.0353,0.0003,0.9968</t>
+  </si>
+  <si>
+    <t>0.1091,0.0048,0.0011,0.9611</t>
+  </si>
+  <si>
+    <t>0.0014,0.0004,0.0004,0.9991</t>
+  </si>
+  <si>
+    <t>0.0007,0.0029,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.3878,0.1382,0.0257,0.3499</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
         <v>264</v>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2023,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
         <v>269</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2415,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
         <v>297</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3339,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
         <v>363</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>425</v>
@@ -4221,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
         <v>426</v>
@@ -4249,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D166" t="s">
         <v>428</v>
@@ -4277,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D168" t="s">
         <v>430</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4767,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
         <v>465</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4907,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D213" t="s">
         <v>475</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5243,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
         <v>499</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
